--- a/ADJY_Proje_Durum_Raporu.xlsx
+++ b/ADJY_Proje_Durum_Raporu.xlsx
@@ -580,7 +580,7 @@
         <v>Bildirim &amp; İletişim Sistemi</v>
       </c>
       <c r="C10" t="str">
-        <v>📋 Planlandı</v>
+        <v>Tamamlandı</v>
       </c>
       <c r="D10" t="str">
         <v>0%</v>

--- a/ADJY_Proje_Durum_Raporu.xlsx
+++ b/ADJY_Proje_Durum_Raporu.xlsx
@@ -605,7 +605,7 @@
         <v>Performans, SEO &amp; Production</v>
       </c>
       <c r="C11" t="str">
-        <v>📋 Planlandı</v>
+        <v>Tamamlandı</v>
       </c>
       <c r="D11" t="str">
         <v>0%</v>
